--- a/data/sources/PSBP_Master_Animal_Signage.xlsx
+++ b/data/sources/PSBP_Master_Animal_Signage.xlsx
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>Present in Florida year-round, with peak nesting activity from fall through spring. Park sightings are occasional flyovers or perched birds.</t>
+          <t>Present in Florida year-round, with peak nesting activity from fall through spring. Many of Florida's nesting adults head north for the summer, making late fall through spring the best window to spot one over the park. Park sightings are occasional flyovers or perched birds.</t>
         </is>
       </c>
       <c r="W18" s="12" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t>Year-round resident in Florida, with additional migrants and wintering birds. Often seen flying over or perched near water.</t>
+          <t>Florida's own ospreys are largely year-round residents, joined each winter by migrants from farther north. Often seen flying over or perched near water.</t>
         </is>
       </c>
       <c r="W19" s="12" t="inlineStr">
@@ -5751,7 +5751,7 @@
 Bill: Stout, heavy, and black — noticeably thicker than other herons'.
 Young: Brown with fine white spots and streaks.
 Posture: Hunched and forward-leaning.
-What to Look For: A compact gray heron with a striking black-and-white face, often standing hunched at the water's edge. The heavy bill and bold face pattern set it apart from the lankier, plainer herons; young birds are brown and spotted.</t>
+What to Look For: A compact gray heron with a striking black-and-white face, often hunched at the water's edge while hunting — though it stands more upright and longer-legged when walking. The heavy bill and bold face pattern set it apart from the lankier, plainer herons; young birds are brown and spotted.</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t>Year-round resident. Often solitary and well hidden, so it rewards a patient, careful look at pond margins.</t>
+          <t>Year-round resident, but much more active and vocal in the spring and summer breeding season — quieter and more stealthy in winter. Often solitary and well hidden, so it rewards a patient, careful look at pond margins.</t>
         </is>
       </c>
       <c r="W29" s="12" t="inlineStr">
